--- a/ENTREGA FINAL/02 - Presupuesto financiero.xlsx
+++ b/ENTREGA FINAL/02 - Presupuesto financiero.xlsx
@@ -5101,19 +5101,19 @@
         </is>
       </c>
       <c r="E30" s="28">
-        <f>('Costos Fijos'!O32-'Costos Fijos'!C21*12+'Costos Variables'!O14)*$C$6</f>
+        <f>('Costos Fijos'!O30-'Costos Fijos'!C16*12+'Costos Variables'!O14)*$C$6</f>
         <v/>
       </c>
       <c r="F30" s="28">
-        <f>('Costos Fijos'!O60-'Costos Fijos'!D21*12+'Costos Variables'!O24)*$C$6</f>
+        <f>('Costos Fijos'!O45-'Costos Fijos'!D16*12+'Costos Variables'!O24)*$C$6</f>
         <v/>
       </c>
       <c r="G30" s="28">
-        <f>('Costos Fijos'!O88-'Costos Fijos'!E21*12+'Costos Variables'!O34)*$C$6</f>
+        <f>('Costos Fijos'!O60-'Costos Fijos'!E16*12+'Costos Variables'!O34)*$C$6</f>
         <v/>
       </c>
       <c r="H30" s="28">
-        <f>('Costos Fijos'!O116-'Costos Fijos'!F21*12+'Costos Variables'!O44)*$C$6</f>
+        <f>('Costos Fijos'!O75-'Costos Fijos'!F16*12+'Costos Variables'!O44)*$C$6</f>
         <v/>
       </c>
       <c r="J30" s="24" t="inlineStr">
@@ -5129,19 +5129,19 @@
         </is>
       </c>
       <c r="E31" s="28">
-        <f>'Costos Fijos'!C21*12*$C$16</f>
+        <f>'Costos Fijos'!C16*12*$C$16</f>
         <v/>
       </c>
       <c r="F31" s="28">
-        <f>'Costos Fijos'!D21*12*$C$16</f>
+        <f>'Costos Fijos'!D16*12*$C$16</f>
         <v/>
       </c>
       <c r="G31" s="28">
-        <f>'Costos Fijos'!E21*12*$C$16</f>
+        <f>'Costos Fijos'!E16*12*$C$16</f>
         <v/>
       </c>
       <c r="H31" s="28">
-        <f>'Costos Fijos'!F21*12*$C$16</f>
+        <f>'Costos Fijos'!F16*12*$C$16</f>
         <v/>
       </c>
       <c r="J31" s="24" t="inlineStr">
@@ -5255,19 +5255,19 @@
         </is>
       </c>
       <c r="E37" s="28">
-        <f>'Costos Fijos'!C21*12*$C$17*(1-$C$18)</f>
+        <f>'Costos Fijos'!C16*12*$C$17*(1-$C$18)</f>
         <v/>
       </c>
       <c r="F37" s="28">
-        <f>'Costos Fijos'!D21*12*$C$17*(1-$C$18)</f>
+        <f>'Costos Fijos'!D16*12*$C$17*(1-$C$18)</f>
         <v/>
       </c>
       <c r="G37" s="28">
-        <f>'Costos Fijos'!E21*12*$C$17*(1-$C$18)</f>
+        <f>'Costos Fijos'!E16*12*$C$17*(1-$C$18)</f>
         <v/>
       </c>
       <c r="H37" s="28">
-        <f>'Costos Fijos'!F21*12*$C$17*(1-$C$18)</f>
+        <f>'Costos Fijos'!F16*12*$C$17*(1-$C$18)</f>
         <v/>
       </c>
       <c r="J37" s="24" t="inlineStr">
@@ -6110,19 +6110,19 @@
         </is>
       </c>
       <c r="E20" s="28">
-        <f>('Costos Fijos'!C15*12)+'RRHH'!O41+'RRHH'!O44</f>
+        <f>('Costos Fijos'!C10*12)+'RRHH'!O41+'RRHH'!O44</f>
         <v/>
       </c>
       <c r="F20" s="28">
-        <f>('Costos Fijos'!D15*12)+'RRHH'!O56+'RRHH'!O59</f>
+        <f>('Costos Fijos'!D10*12)+'RRHH'!O56+'RRHH'!O59</f>
         <v/>
       </c>
       <c r="G20" s="28">
-        <f>('Costos Fijos'!E15*12)+'RRHH'!O71+'RRHH'!O74</f>
+        <f>('Costos Fijos'!E10*12)+'RRHH'!O71+'RRHH'!O74</f>
         <v/>
       </c>
       <c r="H20" s="28">
-        <f>('Costos Fijos'!F15*12)+'RRHH'!O86+'RRHH'!O89</f>
+        <f>('Costos Fijos'!F10*12)+'RRHH'!O86+'RRHH'!O89</f>
         <v/>
       </c>
       <c r="J20" s="24" t="inlineStr">
@@ -19720,51 +19720,51 @@
         </is>
       </c>
       <c r="C10" s="28">
-        <f>'Costos Fijos'!C32</f>
+        <f>'Costos Fijos'!C30</f>
         <v/>
       </c>
       <c r="D10" s="28">
-        <f>'Costos Fijos'!D32</f>
+        <f>'Costos Fijos'!D30</f>
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>'Costos Fijos'!E32</f>
+        <f>'Costos Fijos'!E30</f>
         <v/>
       </c>
       <c r="F10" s="28">
-        <f>'Costos Fijos'!F32</f>
+        <f>'Costos Fijos'!F30</f>
         <v/>
       </c>
       <c r="G10" s="28">
-        <f>'Costos Fijos'!G32</f>
+        <f>'Costos Fijos'!G30</f>
         <v/>
       </c>
       <c r="H10" s="28">
-        <f>'Costos Fijos'!H32</f>
+        <f>'Costos Fijos'!H30</f>
         <v/>
       </c>
       <c r="I10" s="28">
-        <f>'Costos Fijos'!I32</f>
+        <f>'Costos Fijos'!I30</f>
         <v/>
       </c>
       <c r="J10" s="28">
-        <f>'Costos Fijos'!J32</f>
+        <f>'Costos Fijos'!J30</f>
         <v/>
       </c>
       <c r="K10" s="28">
-        <f>'Costos Fijos'!K32</f>
+        <f>'Costos Fijos'!K30</f>
         <v/>
       </c>
       <c r="L10" s="28">
-        <f>'Costos Fijos'!L32</f>
+        <f>'Costos Fijos'!L30</f>
         <v/>
       </c>
       <c r="M10" s="28">
-        <f>'Costos Fijos'!M32</f>
+        <f>'Costos Fijos'!M30</f>
         <v/>
       </c>
       <c r="N10" s="28">
-        <f>'Costos Fijos'!N32</f>
+        <f>'Costos Fijos'!N30</f>
         <v/>
       </c>
       <c r="O10" s="29">
@@ -20176,51 +20176,51 @@
         </is>
       </c>
       <c r="C23" s="28">
-        <f>'Costos Fijos'!C60</f>
+        <f>'Costos Fijos'!C45</f>
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>'Costos Fijos'!D60</f>
+        <f>'Costos Fijos'!D45</f>
         <v/>
       </c>
       <c r="E23" s="28">
-        <f>'Costos Fijos'!E60</f>
+        <f>'Costos Fijos'!E45</f>
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>'Costos Fijos'!F60</f>
+        <f>'Costos Fijos'!F45</f>
         <v/>
       </c>
       <c r="G23" s="28">
-        <f>'Costos Fijos'!G60</f>
+        <f>'Costos Fijos'!G45</f>
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>'Costos Fijos'!H60</f>
+        <f>'Costos Fijos'!H45</f>
         <v/>
       </c>
       <c r="I23" s="28">
-        <f>'Costos Fijos'!I60</f>
+        <f>'Costos Fijos'!I45</f>
         <v/>
       </c>
       <c r="J23" s="28">
-        <f>'Costos Fijos'!J60</f>
+        <f>'Costos Fijos'!J45</f>
         <v/>
       </c>
       <c r="K23" s="28">
-        <f>'Costos Fijos'!K60</f>
+        <f>'Costos Fijos'!K45</f>
         <v/>
       </c>
       <c r="L23" s="28">
-        <f>'Costos Fijos'!L60</f>
+        <f>'Costos Fijos'!L45</f>
         <v/>
       </c>
       <c r="M23" s="28">
-        <f>'Costos Fijos'!M60</f>
+        <f>'Costos Fijos'!M45</f>
         <v/>
       </c>
       <c r="N23" s="28">
-        <f>'Costos Fijos'!N60</f>
+        <f>'Costos Fijos'!N45</f>
         <v/>
       </c>
       <c r="O23" s="29">
@@ -20632,51 +20632,51 @@
         </is>
       </c>
       <c r="C36" s="28">
-        <f>'Costos Fijos'!C88</f>
+        <f>'Costos Fijos'!C60</f>
         <v/>
       </c>
       <c r="D36" s="28">
-        <f>'Costos Fijos'!D88</f>
+        <f>'Costos Fijos'!D60</f>
         <v/>
       </c>
       <c r="E36" s="28">
-        <f>'Costos Fijos'!E88</f>
+        <f>'Costos Fijos'!E60</f>
         <v/>
       </c>
       <c r="F36" s="28">
-        <f>'Costos Fijos'!F88</f>
+        <f>'Costos Fijos'!F60</f>
         <v/>
       </c>
       <c r="G36" s="28">
-        <f>'Costos Fijos'!G88</f>
+        <f>'Costos Fijos'!G60</f>
         <v/>
       </c>
       <c r="H36" s="28">
-        <f>'Costos Fijos'!H88</f>
+        <f>'Costos Fijos'!H60</f>
         <v/>
       </c>
       <c r="I36" s="28">
-        <f>'Costos Fijos'!I88</f>
+        <f>'Costos Fijos'!I60</f>
         <v/>
       </c>
       <c r="J36" s="28">
-        <f>'Costos Fijos'!J88</f>
+        <f>'Costos Fijos'!J60</f>
         <v/>
       </c>
       <c r="K36" s="28">
-        <f>'Costos Fijos'!K88</f>
+        <f>'Costos Fijos'!K60</f>
         <v/>
       </c>
       <c r="L36" s="28">
-        <f>'Costos Fijos'!L88</f>
+        <f>'Costos Fijos'!L60</f>
         <v/>
       </c>
       <c r="M36" s="28">
-        <f>'Costos Fijos'!M88</f>
+        <f>'Costos Fijos'!M60</f>
         <v/>
       </c>
       <c r="N36" s="28">
-        <f>'Costos Fijos'!N88</f>
+        <f>'Costos Fijos'!N60</f>
         <v/>
       </c>
       <c r="O36" s="29">
@@ -21088,51 +21088,51 @@
         </is>
       </c>
       <c r="C49" s="28">
-        <f>'Costos Fijos'!C116</f>
+        <f>'Costos Fijos'!C75</f>
         <v/>
       </c>
       <c r="D49" s="28">
-        <f>'Costos Fijos'!D116</f>
+        <f>'Costos Fijos'!D75</f>
         <v/>
       </c>
       <c r="E49" s="28">
-        <f>'Costos Fijos'!E116</f>
+        <f>'Costos Fijos'!E75</f>
         <v/>
       </c>
       <c r="F49" s="28">
-        <f>'Costos Fijos'!F116</f>
+        <f>'Costos Fijos'!F75</f>
         <v/>
       </c>
       <c r="G49" s="28">
-        <f>'Costos Fijos'!G116</f>
+        <f>'Costos Fijos'!G75</f>
         <v/>
       </c>
       <c r="H49" s="28">
-        <f>'Costos Fijos'!H116</f>
+        <f>'Costos Fijos'!H75</f>
         <v/>
       </c>
       <c r="I49" s="28">
-        <f>'Costos Fijos'!I116</f>
+        <f>'Costos Fijos'!I75</f>
         <v/>
       </c>
       <c r="J49" s="28">
-        <f>'Costos Fijos'!J116</f>
+        <f>'Costos Fijos'!J75</f>
         <v/>
       </c>
       <c r="K49" s="28">
-        <f>'Costos Fijos'!K116</f>
+        <f>'Costos Fijos'!K75</f>
         <v/>
       </c>
       <c r="L49" s="28">
-        <f>'Costos Fijos'!L116</f>
+        <f>'Costos Fijos'!L75</f>
         <v/>
       </c>
       <c r="M49" s="28">
-        <f>'Costos Fijos'!M116</f>
+        <f>'Costos Fijos'!M75</f>
         <v/>
       </c>
       <c r="N49" s="28">
-        <f>'Costos Fijos'!N116</f>
+        <f>'Costos Fijos'!N75</f>
         <v/>
       </c>
       <c r="O49" s="29">
@@ -21476,7 +21476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U116"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21569,6 +21569,24 @@
       </c>
     </row>
     <row r="5">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Importe mensual por año (celdas de entrada)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
       <c r="Q5" s="20" t="inlineStr">
         <is>
           <t>Concepto</t>
@@ -21588,167 +21606,267 @@
       </c>
     </row>
     <row r="6">
+      <c r="C6" s="11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>CAPEX / OPEX</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Origen</t>
+        </is>
+      </c>
       <c r="Q6" s="13" t="inlineStr">
         <is>
           <t>Total de costos fijos</t>
         </is>
       </c>
       <c r="R6" s="28">
-        <f>O32</f>
+        <f>O30</f>
         <v/>
       </c>
       <c r="S6" s="28">
+        <f>O45</f>
+        <v/>
+      </c>
+      <c r="T6" s="28">
         <f>O60</f>
         <v/>
       </c>
-      <c r="T6" s="28">
-        <f>O88</f>
-        <v/>
-      </c>
       <c r="U6" s="28">
-        <f>O116</f>
+        <f>O75</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="5" t="n">
-        <v>2027</v>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura en la nube (base)</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>430000</v>
+      </c>
+      <c r="G7" s="37" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="H7" s="37" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>AWS o Azure. La Clase 3 lo clasifica como OPEX: no se activa, se consume</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Ene</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>Abr</t>
-        </is>
-      </c>
-      <c r="G8" s="26" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="I8" s="26" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="J8" s="26" t="inlineStr">
-        <is>
-          <t>Ago</t>
-        </is>
-      </c>
-      <c r="K8" s="26" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="M8" s="26" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="N8" s="26" t="inlineStr">
-        <is>
-          <t>Dic</t>
-        </is>
-      </c>
-      <c r="O8" s="27" t="inlineStr">
-        <is>
-          <t>Total 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Herramientas y licencias de desarrollo</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G8" s="37" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="H8" s="37" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>GitHub, Jira y similares. SaaS del exterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Herramientas de IA del equipo</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="H9" s="37" t="inlineStr">
+        <is>
+          <t>Exterior</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Claude Teams y asistentes de código, una licencia por persona de desarrollo y soporte. Es el gasto que más creció en el sector y no estaba en el modelo</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Importe mensual por año (celdas de entrada)</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="n"/>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Marketing y contenidos</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>260000</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>340000</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>420000</v>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="H10" s="37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Pauta, contenidos y herramientas de campaña</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="C11" s="11" t="n">
-        <v>2027</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>2028</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>2029</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>2030</v>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>CAPEX / OPEX</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>Origen</t>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Estudio contable y legales</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>170000</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>210000</v>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="H11" s="37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Honorarios mensuales del estudio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Infraestructura en la nube (base)</t>
+          <t>Espacio de trabajo y telefonía</t>
         </is>
       </c>
       <c r="C12" s="15" t="n">
-        <v>120000</v>
+        <v>45000</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>200000</v>
+        <v>68000</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>320000</v>
+        <v>105000</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>430000</v>
+        <v>145000</v>
       </c>
       <c r="G12" s="37" t="inlineStr">
         <is>
@@ -21757,37 +21875,37 @@
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>AWS o Azure. La Clase 3 lo clasifica como OPEX: no se activa, se consume</t>
+          <t>Coworking por puesto y telefonía. No hay inmueble propio, así que el modelo no tiene impuesto inmobiliario</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Herramientas y licencias de desarrollo</t>
+          <t>Conectividad del equipo remoto</t>
         </is>
       </c>
       <c r="C13" s="15" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D13" s="15" t="n">
         <v>40000</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="E13" s="15" t="n">
         <v>60000</v>
       </c>
-      <c r="E13" s="15" t="n">
-        <v>90000</v>
-      </c>
       <c r="F13" s="15" t="n">
-        <v>120000</v>
+        <v>84000</v>
       </c>
       <c r="G13" s="37" t="inlineStr">
         <is>
@@ -21796,320 +21914,326 @@
       </c>
       <c r="H13" s="37" t="inlineStr">
         <is>
-          <t>Exterior</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>GitHub, Jira y similares. SaaS del exterior</t>
+          <t>Reintegro de internet a cada persona: el equipo trabaja remoto y la conexión es una condición de trabajo, no un gasto personal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Otros gastos operativos</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G14" s="37" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Bancarios, papelería, imprevistos menores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Total mensual</t>
+        </is>
+      </c>
+      <c r="C15" s="18">
+        <f>SUM(C7:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="18">
+        <f>SUM(D7:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>SUM(E7:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="18">
+        <f>SUM(F7:F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    del cual se paga al exterior</t>
+        </is>
+      </c>
+      <c r="C16" s="28">
+        <f>SUMIF($H$7:$H$14,"Exterior",C7:C14)</f>
+        <v/>
+      </c>
+      <c r="D16" s="28">
+        <f>SUMIF($H$7:$H$14,"Exterior",D7:D14)</f>
+        <v/>
+      </c>
+      <c r="E16" s="28">
+        <f>SUMIF($H$7:$H$14,"Exterior",E7:E14)</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>SUMIF($H$7:$H$14,"Exterior",F7:F14)</f>
+        <v/>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Servicios digitales importados: nube, licencias y herramientas de IA. La hoja Impuestos les aplica el IVA acrecentado y la retención a beneficiarios del exterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="C18" s="5" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="inlineStr">
+        <is>
+          <t>Ago</t>
+        </is>
+      </c>
+      <c r="K19" s="26" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="M19" s="26" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="N19" s="26" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="O19" s="27" t="inlineStr">
+        <is>
+          <t>Total 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Desarrollo mensual</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas de IA del equipo</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>140000</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>260000</v>
-      </c>
-      <c r="G14" s="37" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="H14" s="37" t="inlineStr">
-        <is>
-          <t>Exterior</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Claude Teams y asistentes de código, una licencia por persona de desarrollo y soporte. Es el gasto que más creció en el sector y no estaba en el modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Marketing y contenidos</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>175000</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>260000</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>340000</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>420000</v>
-      </c>
-      <c r="G15" s="37" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="H15" s="37" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Pauta, contenidos y herramientas de campaña</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Administración</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Estudio contable y legales</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>105000</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>130000</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>170000</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>210000</v>
-      </c>
-      <c r="G16" s="37" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="H16" s="37" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Honorarios mensuales del estudio</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Espacio de trabajo y telefonía</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>68000</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>105000</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>145000</v>
-      </c>
-      <c r="G17" s="37" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="H17" s="37" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>Coworking por puesto y telefonía. No hay inmueble propio, así que el modelo no tiene impuesto inmobiliario</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>24000</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>84000</v>
-      </c>
-      <c r="G18" s="37" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="H18" s="37" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Reintegro de internet a cada persona: el equipo trabaja remoto y la conexión es una condición de trabajo, no un gasto personal</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G19" s="37" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="H19" s="37" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>Bancarios, papelería, imprevistos menores</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>Total mensual</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>SUM(C12:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="18">
-        <f>SUM(D12:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="18">
-        <f>SUM(E12:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="18">
-        <f>SUM(F12:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    del cual se paga al exterior</t>
-        </is>
-      </c>
-      <c r="C21" s="28">
-        <f>SUMIF($H$12:$H$19,"Exterior",C12:C19)</f>
-        <v/>
-      </c>
-      <c r="D21" s="28">
-        <f>SUMIF($H$12:$H$19,"Exterior",D12:D19)</f>
-        <v/>
-      </c>
-      <c r="E21" s="28">
-        <f>SUMIF($H$12:$H$19,"Exterior",E12:E19)</f>
-        <v/>
-      </c>
-      <c r="F21" s="28">
-        <f>SUMIF($H$12:$H$19,"Exterior",F12:F19)</f>
-        <v/>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Servicios digitales importados: nube, licencias y herramientas de IA. La hoja Impuestos les aplica el IVA acrecentado y la retención a beneficiarios del exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura en la nube (base)</t>
+        </is>
+      </c>
+      <c r="C22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="G22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="H22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="I22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="J22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="K22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="L22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="M22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="N22" s="28">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="O22" s="29">
+        <f>SUM(C22:N22)</f>
+        <v/>
+      </c>
+    </row>
     <row r="23">
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Desarrollo mensual</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="10" t="n"/>
-      <c r="N23" s="10" t="n"/>
-      <c r="O23" s="10" t="n"/>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Herramientas y licencias de desarrollo</t>
+        </is>
+      </c>
+      <c r="C23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="F23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="G23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="H23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="I23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="J23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="K23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="L23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="M23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="N23" s="28">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="O23" s="29">
+        <f>SUM(C23:N23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
@@ -22119,55 +22243,55 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Infraestructura en la nube (base)</t>
+          <t>Herramientas de IA del equipo</t>
         </is>
       </c>
       <c r="C24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="E24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="F24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="G24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="I24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="J24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="K24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="L24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="M24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="N24" s="28">
-        <f>$C$12</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="O24" s="29">
@@ -22178,60 +22302,60 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Herramientas y licencias de desarrollo</t>
+          <t>Marketing y contenidos</t>
         </is>
       </c>
       <c r="C25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="E25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="G25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="H25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="I25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="J25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="K25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="L25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="M25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="N25" s="28">
-        <f>$C$13</f>
+        <f>$C$10</f>
         <v/>
       </c>
       <c r="O25" s="29">
@@ -22242,60 +22366,60 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Administración</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Herramientas de IA del equipo</t>
+          <t>Estudio contable y legales</t>
         </is>
       </c>
       <c r="C26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="E26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="F26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="G26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="H26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="I26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="J26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="K26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="L26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="M26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="N26" s="28">
-        <f>$C$14</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="O26" s="29">
@@ -22306,60 +22430,60 @@
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Marketing y contenidos</t>
+          <t>Espacio de trabajo y telefonía</t>
         </is>
       </c>
       <c r="C27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="E27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="F27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="G27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="H27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="I27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="J27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="K27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="L27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="M27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="N27" s="28">
-        <f>$C$15</f>
+        <f>$C$12</f>
         <v/>
       </c>
       <c r="O27" s="29">
@@ -22370,60 +22494,60 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>Administración</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Estudio contable y legales</t>
+          <t>Conectividad del equipo remoto</t>
         </is>
       </c>
       <c r="C28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="D28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="E28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="F28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="G28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="H28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="I28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="J28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="K28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="L28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="M28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="N28" s="28">
-        <f>$C$16</f>
+        <f>$C$13</f>
         <v/>
       </c>
       <c r="O28" s="29">
@@ -22439,55 +22563,55 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Espacio de trabajo y telefonía</t>
+          <t>Otros gastos operativos</t>
         </is>
       </c>
       <c r="C29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="D29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="E29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="F29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="G29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="H29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="I29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="J29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="K29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="L29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="M29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="N29" s="28">
-        <f>$C$17</f>
+        <f>$C$14</f>
         <v/>
       </c>
       <c r="O29" s="29">
@@ -22498,60 +22622,60 @@
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
-      </c>
-      <c r="C30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="D30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="E30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="F30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="G30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="H30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="I30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="J30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="K30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="L30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="M30" s="28">
-        <f>$C$18</f>
-        <v/>
-      </c>
-      <c r="N30" s="28">
-        <f>$C$18</f>
+          <t>COSTOS FIJOS</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Total de costos fijos</t>
+        </is>
+      </c>
+      <c r="C30" s="18">
+        <f>SUM(C22:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>SUM(D22:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="18">
+        <f>SUM(E22:E29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="18">
+        <f>SUM(F22:F29)</f>
+        <v/>
+      </c>
+      <c r="G30" s="18">
+        <f>SUM(G22:G29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="18">
+        <f>SUM(H22:H29)</f>
+        <v/>
+      </c>
+      <c r="I30" s="18">
+        <f>SUM(I22:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="18">
+        <f>SUM(J22:J29)</f>
+        <v/>
+      </c>
+      <c r="K30" s="18">
+        <f>SUM(K22:K29)</f>
+        <v/>
+      </c>
+      <c r="L30" s="18">
+        <f>SUM(L22:L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="18">
+        <f>SUM(M22:M29)</f>
+        <v/>
+      </c>
+      <c r="N30" s="18">
+        <f>SUM(N22:N29)</f>
         <v/>
       </c>
       <c r="O30" s="29">
@@ -22559,337 +22683,748 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-      <c r="C31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="F31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="G31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="H31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="I31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="J31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="K31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="L31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="M31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="N31" s="28">
-        <f>$C$19</f>
-        <v/>
-      </c>
-      <c r="O31" s="29">
-        <f>SUM(C31:N31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>COSTOS FIJOS</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Total de costos fijos</t>
-        </is>
-      </c>
-      <c r="C32" s="18">
-        <f>SUM(C24:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="18">
-        <f>SUM(D24:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="18">
-        <f>SUM(E24:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="18">
-        <f>SUM(F24:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="18">
-        <f>SUM(G24:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="18">
-        <f>SUM(H24:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="18">
-        <f>SUM(I24:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="18">
-        <f>SUM(J24:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="18">
-        <f>SUM(K24:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="18">
-        <f>SUM(L24:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="18">
-        <f>SUM(M24:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="18">
-        <f>SUM(N24:N31)</f>
-        <v/>
-      </c>
-      <c r="O32" s="29">
-        <f>SUM(C32:N32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35">
-      <c r="C35" s="5" t="n">
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="C33" s="5" t="n">
         <v>2028</v>
       </c>
     </row>
+    <row r="34">
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="inlineStr">
+        <is>
+          <t>Ago</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="M34" s="26" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="N34" s="26" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="O34" s="27" t="inlineStr">
+        <is>
+          <t>Total 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>Ene</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="F36" s="26" t="inlineStr">
-        <is>
-          <t>Abr</t>
-        </is>
-      </c>
-      <c r="G36" s="26" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="J36" s="26" t="inlineStr">
-        <is>
-          <t>Ago</t>
-        </is>
-      </c>
-      <c r="K36" s="26" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="M36" s="26" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="N36" s="26" t="inlineStr">
-        <is>
-          <t>Dic</t>
-        </is>
-      </c>
-      <c r="O36" s="27" t="inlineStr">
-        <is>
-          <t>Total 2028</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Desarrollo mensual</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura en la nube (base)</t>
+        </is>
+      </c>
+      <c r="C37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="D37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="E37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="F37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="G37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="H37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="I37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="J37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="K37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="L37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="M37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="N37" s="28">
+        <f>$D$7</f>
+        <v/>
+      </c>
+      <c r="O37" s="29">
+        <f>SUM(C37:N37)</f>
+        <v/>
+      </c>
+    </row>
     <row r="38">
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Importe mensual por año (celdas de entrada)</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
-      <c r="J38" s="10" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="10" t="n"/>
-      <c r="M38" s="10" t="n"/>
-      <c r="N38" s="10" t="n"/>
-      <c r="O38" s="10" t="n"/>
-    </row>
-    <row r="39"/>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Herramientas y licencias de desarrollo</t>
+        </is>
+      </c>
+      <c r="C38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="D38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="E38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="F38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="G38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="H38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="I38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="J38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="K38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="L38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="M38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="N38" s="28">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="O38" s="29">
+        <f>SUM(C38:N38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Herramientas de IA del equipo</t>
+        </is>
+      </c>
+      <c r="C39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="D39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="E39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="F39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="G39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="H39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="I39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="J39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="K39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="L39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="M39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="N39" s="28">
+        <f>$D$9</f>
+        <v/>
+      </c>
+      <c r="O39" s="29">
+        <f>SUM(C39:N39)</f>
+        <v/>
+      </c>
+    </row>
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Infraestructura en la nube (base)</t>
-        </is>
+          <t>Marketing y contenidos</t>
+        </is>
+      </c>
+      <c r="C40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="D40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="E40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="G40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="H40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="I40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="J40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="K40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="L40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="M40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="N40" s="28">
+        <f>$D$10</f>
+        <v/>
+      </c>
+      <c r="O40" s="29">
+        <f>SUM(C40:N40)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Administración</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Herramientas y licencias de desarrollo</t>
-        </is>
+          <t>Estudio contable y legales</t>
+        </is>
+      </c>
+      <c r="C41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="D41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="E41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="F41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="G41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="H41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="I41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="J41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="K41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="L41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="M41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="N41" s="28">
+        <f>$D$11</f>
+        <v/>
+      </c>
+      <c r="O41" s="29">
+        <f>SUM(C41:N41)</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Herramientas de IA del equipo</t>
-        </is>
+          <t>Espacio de trabajo y telefonía</t>
+        </is>
+      </c>
+      <c r="C42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="D42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="G42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="H42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="I42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="J42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="K42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="L42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="M42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="N42" s="28">
+        <f>$D$12</f>
+        <v/>
+      </c>
+      <c r="O42" s="29">
+        <f>SUM(C42:N42)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Marketing y contenidos</t>
-        </is>
+          <t>Conectividad del equipo remoto</t>
+        </is>
+      </c>
+      <c r="C43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="D43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="E43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="F43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="G43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="H43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="I43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="J43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="K43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="L43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="M43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="N43" s="28">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="O43" s="29">
+        <f>SUM(C43:N43)</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>Administración</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Estudio contable y legales</t>
-        </is>
+          <t>Otros gastos operativos</t>
+        </is>
+      </c>
+      <c r="C44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="D44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="E44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="F44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="G44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="H44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="I44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="J44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="K44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="L44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="M44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="N44" s="28">
+        <f>$D$14</f>
+        <v/>
+      </c>
+      <c r="O44" s="29">
+        <f>SUM(C44:N44)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>Espacio de trabajo y telefonía</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-    </row>
+          <t>COSTOS FIJOS</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Total de costos fijos</t>
+        </is>
+      </c>
+      <c r="C45" s="18">
+        <f>SUM(C37:C44)</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f>SUM(D37:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="18">
+        <f>SUM(E37:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>SUM(F37:F44)</f>
+        <v/>
+      </c>
+      <c r="G45" s="18">
+        <f>SUM(G37:G44)</f>
+        <v/>
+      </c>
+      <c r="H45" s="18">
+        <f>SUM(H37:H44)</f>
+        <v/>
+      </c>
+      <c r="I45" s="18">
+        <f>SUM(I37:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="18">
+        <f>SUM(J37:J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="18">
+        <f>SUM(K37:K44)</f>
+        <v/>
+      </c>
+      <c r="L45" s="18">
+        <f>SUM(L37:L44)</f>
+        <v/>
+      </c>
+      <c r="M45" s="18">
+        <f>SUM(M37:M44)</f>
+        <v/>
+      </c>
+      <c r="N45" s="18">
+        <f>SUM(N37:N44)</f>
+        <v/>
+      </c>
+      <c r="O45" s="29">
+        <f>SUM(C45:N45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>Total mensual</t>
-        </is>
+      <c r="C48" s="5" t="n">
+        <v>2029</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    del cual se paga al exterior</t>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="inlineStr">
+        <is>
+          <t>Ago</t>
+        </is>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="N49" s="26" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="O49" s="27" t="inlineStr">
+        <is>
+          <t>Total 2029</t>
         </is>
       </c>
     </row>
@@ -22926,51 +23461,51 @@
         </is>
       </c>
       <c r="C52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="D52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="E52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="F52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="G52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="H52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="I52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="J52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="K52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="L52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="M52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="N52" s="28">
-        <f>$D$12</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="O52" s="29">
@@ -22990,51 +23525,51 @@
         </is>
       </c>
       <c r="C53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="D53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="E53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="F53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="G53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="H53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="I53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="J53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="K53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="L53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="M53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="N53" s="28">
-        <f>$D$13</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="O53" s="29">
@@ -23054,51 +23589,51 @@
         </is>
       </c>
       <c r="C54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="D54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="E54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="F54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="G54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="H54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="I54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="J54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="K54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="L54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="M54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="N54" s="28">
-        <f>$D$14</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="O54" s="29">
@@ -23118,51 +23653,51 @@
         </is>
       </c>
       <c r="C55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="D55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="E55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="F55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="G55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="H55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="I55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="J55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="K55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="L55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="M55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="N55" s="28">
-        <f>$D$15</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="O55" s="29">
@@ -23182,51 +23717,51 @@
         </is>
       </c>
       <c r="C56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="D56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="E56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="F56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="G56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="H56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="I56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="J56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="K56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="L56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="M56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="N56" s="28">
-        <f>$D$16</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="O56" s="29">
@@ -23246,51 +23781,51 @@
         </is>
       </c>
       <c r="C57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="D57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="E57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="F57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="G57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="H57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="I57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="J57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="K57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="L57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="M57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="N57" s="28">
-        <f>$D$17</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="O57" s="29">
@@ -23310,51 +23845,51 @@
         </is>
       </c>
       <c r="C58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="D58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="E58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="F58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="G58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="H58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="I58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="J58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="K58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="L58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="M58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="N58" s="28">
-        <f>$D$18</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="O58" s="29">
@@ -23374,51 +23909,51 @@
         </is>
       </c>
       <c r="C59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="D59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="E59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="F59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="G59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="H59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="I59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="J59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="K59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="L59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="M59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="N59" s="28">
-        <f>$D$19</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="O59" s="29">
@@ -23494,7 +24029,7 @@
     <row r="62"/>
     <row r="63">
       <c r="C63" s="5" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="64">
@@ -23560,7 +24095,7 @@
       </c>
       <c r="O64" s="27" t="inlineStr">
         <is>
-          <t>Total 2029</t>
+          <t>Total 2030</t>
         </is>
       </c>
     </row>
@@ -23568,7 +24103,7 @@
     <row r="66">
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Importe mensual por año (celdas de entrada)</t>
+          <t>Desarrollo mensual</t>
         </is>
       </c>
       <c r="C66" s="10" t="n"/>
@@ -23585,7 +24120,70 @@
       <c r="N66" s="10" t="n"/>
       <c r="O66" s="10" t="n"/>
     </row>
-    <row r="67"/>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Infraestructura en la nube (base)</t>
+        </is>
+      </c>
+      <c r="C67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="D67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="E67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="F67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="G67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="H67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="I67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="J67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="K67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="L67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="M67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="N67" s="28">
+        <f>$F$7</f>
+        <v/>
+      </c>
+      <c r="O67" s="29">
+        <f>SUM(C67:N67)</f>
+        <v/>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" s="20" t="inlineStr">
         <is>
@@ -23594,8 +24192,60 @@
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>Infraestructura en la nube (base)</t>
-        </is>
+          <t>Herramientas y licencias de desarrollo</t>
+        </is>
+      </c>
+      <c r="C68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="D68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="E68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="F68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="G68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="H68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="I68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="J68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="K68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="L68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="M68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="N68" s="28">
+        <f>$F$8</f>
+        <v/>
+      </c>
+      <c r="O68" s="29">
+        <f>SUM(C68:N68)</f>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -23606,44 +24256,252 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>Herramientas y licencias de desarrollo</t>
-        </is>
+          <t>Herramientas de IA del equipo</t>
+        </is>
+      </c>
+      <c r="C69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="D69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="E69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="F69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="G69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="H69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="I69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="J69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="K69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="L69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="M69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="N69" s="28">
+        <f>$F$9</f>
+        <v/>
+      </c>
+      <c r="O69" s="29">
+        <f>SUM(C69:N69)</f>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>Herramientas de IA del equipo</t>
-        </is>
+          <t>Marketing y contenidos</t>
+        </is>
+      </c>
+      <c r="C70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="D70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="E70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="F70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="G70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="H70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="I70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="J70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="K70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="L70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="M70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="N70" s="28">
+        <f>$F$10</f>
+        <v/>
+      </c>
+      <c r="O70" s="29">
+        <f>SUM(C70:N70)</f>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Administración</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>Marketing y contenidos</t>
-        </is>
+          <t>Estudio contable y legales</t>
+        </is>
+      </c>
+      <c r="C71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="D71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="E71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="F71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="G71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="H71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="I71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="J71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="K71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="L71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="M71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="N71" s="28">
+        <f>$F$11</f>
+        <v/>
+      </c>
+      <c r="O71" s="29">
+        <f>SUM(C71:N71)</f>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Administración</t>
+          <t>Operación</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>Estudio contable y legales</t>
-        </is>
+          <t>Espacio de trabajo y telefonía</t>
+        </is>
+      </c>
+      <c r="C72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="D72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="E72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="F72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="G72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="H72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="I72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="J72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="K72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="L72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="M72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="N72" s="28">
+        <f>$F$12</f>
+        <v/>
+      </c>
+      <c r="O72" s="29">
+        <f>SUM(C72:N72)</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -23654,8 +24512,60 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>Espacio de trabajo y telefonía</t>
-        </is>
+          <t>Conectividad del equipo remoto</t>
+        </is>
+      </c>
+      <c r="C73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="D73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="E73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="F73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="G73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="H73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="I73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="J73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="K73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="L73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="M73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="N73" s="28">
+        <f>$F$13</f>
+        <v/>
+      </c>
+      <c r="O73" s="29">
+        <f>SUM(C73:N73)</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -23666,1433 +24576,123 @@
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
+          <t>Otros gastos operativos</t>
+        </is>
+      </c>
+      <c r="C74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="D74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="E74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="F74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="G74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="H74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="I74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="J74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="K74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="L74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="M74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="N74" s="28">
+        <f>$F$14</f>
+        <v/>
+      </c>
+      <c r="O74" s="29">
+        <f>SUM(C74:N74)</f>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="20" t="inlineStr">
-        <is>
-          <t>Total mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    del cual se paga al exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Desarrollo mensual</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="n"/>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>Infraestructura en la nube (base)</t>
-        </is>
-      </c>
-      <c r="C80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="D80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="E80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="F80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="G80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="H80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="I80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="J80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="K80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="L80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="M80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="N80" s="28">
-        <f>$E$12</f>
-        <v/>
-      </c>
-      <c r="O80" s="29">
-        <f>SUM(C80:N80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas y licencias de desarrollo</t>
-        </is>
-      </c>
-      <c r="C81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="D81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="E81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="F81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="G81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="H81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="I81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="J81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="K81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="L81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="M81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="N81" s="28">
-        <f>$E$13</f>
-        <v/>
-      </c>
-      <c r="O81" s="29">
-        <f>SUM(C81:N81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas de IA del equipo</t>
-        </is>
-      </c>
-      <c r="C82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="D82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="E82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="F82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="G82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="H82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="I82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="J82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="K82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="L82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="M82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="N82" s="28">
-        <f>$E$14</f>
-        <v/>
-      </c>
-      <c r="O82" s="29">
-        <f>SUM(C82:N82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="20" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>Marketing y contenidos</t>
-        </is>
-      </c>
-      <c r="C83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="D83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="E83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="F83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="G83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="H83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="I83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="J83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="K83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="L83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="M83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="N83" s="28">
-        <f>$E$15</f>
-        <v/>
-      </c>
-      <c r="O83" s="29">
-        <f>SUM(C83:N83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>Administración</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
-        <is>
-          <t>Estudio contable y legales</t>
-        </is>
-      </c>
-      <c r="C84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="D84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="E84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="F84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="G84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="H84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="I84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="J84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="K84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="L84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="M84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="N84" s="28">
-        <f>$E$16</f>
-        <v/>
-      </c>
-      <c r="O84" s="29">
-        <f>SUM(C84:N84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="inlineStr">
-        <is>
-          <t>Espacio de trabajo y telefonía</t>
-        </is>
-      </c>
-      <c r="C85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="D85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="E85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="F85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="G85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="H85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="I85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="J85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="K85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="L85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="M85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="N85" s="28">
-        <f>$E$17</f>
-        <v/>
-      </c>
-      <c r="O85" s="29">
-        <f>SUM(C85:N85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
-      </c>
-      <c r="C86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="D86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="E86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="F86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="G86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="H86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="I86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="J86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="K86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="L86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="M86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="N86" s="28">
-        <f>$E$18</f>
-        <v/>
-      </c>
-      <c r="O86" s="29">
-        <f>SUM(C86:N86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-      <c r="C87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="D87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="E87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="F87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="G87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="H87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="I87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="J87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="K87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="L87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="M87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="N87" s="28">
-        <f>$E$19</f>
-        <v/>
-      </c>
-      <c r="O87" s="29">
-        <f>SUM(C87:N87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
           <t>COSTOS FIJOS</t>
         </is>
       </c>
-      <c r="B88" s="20" t="inlineStr">
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>Total de costos fijos</t>
         </is>
       </c>
-      <c r="C88" s="18">
-        <f>SUM(C80:C87)</f>
-        <v/>
-      </c>
-      <c r="D88" s="18">
-        <f>SUM(D80:D87)</f>
-        <v/>
-      </c>
-      <c r="E88" s="18">
-        <f>SUM(E80:E87)</f>
-        <v/>
-      </c>
-      <c r="F88" s="18">
-        <f>SUM(F80:F87)</f>
-        <v/>
-      </c>
-      <c r="G88" s="18">
-        <f>SUM(G80:G87)</f>
-        <v/>
-      </c>
-      <c r="H88" s="18">
-        <f>SUM(H80:H87)</f>
-        <v/>
-      </c>
-      <c r="I88" s="18">
-        <f>SUM(I80:I87)</f>
-        <v/>
-      </c>
-      <c r="J88" s="18">
-        <f>SUM(J80:J87)</f>
-        <v/>
-      </c>
-      <c r="K88" s="18">
-        <f>SUM(K80:K87)</f>
-        <v/>
-      </c>
-      <c r="L88" s="18">
-        <f>SUM(L80:L87)</f>
-        <v/>
-      </c>
-      <c r="M88" s="18">
-        <f>SUM(M80:M87)</f>
-        <v/>
-      </c>
-      <c r="N88" s="18">
-        <f>SUM(N80:N87)</f>
-        <v/>
-      </c>
-      <c r="O88" s="29">
-        <f>SUM(C88:N88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91">
-      <c r="C91" s="5" t="n">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="C92" s="26" t="inlineStr">
-        <is>
-          <t>Ene</t>
-        </is>
-      </c>
-      <c r="D92" s="26" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="E92" s="26" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="F92" s="26" t="inlineStr">
-        <is>
-          <t>Abr</t>
-        </is>
-      </c>
-      <c r="G92" s="26" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="H92" s="26" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="I92" s="26" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="J92" s="26" t="inlineStr">
-        <is>
-          <t>Ago</t>
-        </is>
-      </c>
-      <c r="K92" s="26" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="L92" s="26" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="M92" s="26" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="N92" s="26" t="inlineStr">
-        <is>
-          <t>Dic</t>
-        </is>
-      </c>
-      <c r="O92" s="27" t="inlineStr">
-        <is>
-          <t>Total 2030</t>
-        </is>
-      </c>
-    </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>Importe mensual por año (celdas de entrada)</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-    </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>Infraestructura en la nube (base)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas y licencias de desarrollo</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas de IA del equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>Marketing y contenidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>Administración</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>Estudio contable y legales</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>Espacio de trabajo y telefonía</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
-        <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="20" t="inlineStr">
-        <is>
-          <t>Total mensual</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    del cual se paga al exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="106"/>
-    <row r="107">
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>Desarrollo mensual</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="n"/>
-      <c r="D107" s="10" t="n"/>
-      <c r="E107" s="10" t="n"/>
-      <c r="F107" s="10" t="n"/>
-      <c r="G107" s="10" t="n"/>
-      <c r="H107" s="10" t="n"/>
-      <c r="I107" s="10" t="n"/>
-      <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
-      <c r="L107" s="10" t="n"/>
-      <c r="M107" s="10" t="n"/>
-      <c r="N107" s="10" t="n"/>
-      <c r="O107" s="10" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>Infraestructura en la nube (base)</t>
-        </is>
-      </c>
-      <c r="C108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="D108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="E108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="F108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="G108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="H108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="I108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="J108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="K108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="L108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="M108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="N108" s="28">
-        <f>$F$12</f>
-        <v/>
-      </c>
-      <c r="O108" s="29">
-        <f>SUM(C108:N108)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas y licencias de desarrollo</t>
-        </is>
-      </c>
-      <c r="C109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="D109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="E109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="F109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="G109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="H109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="I109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="J109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="K109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="L109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="M109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="N109" s="28">
-        <f>$F$13</f>
-        <v/>
-      </c>
-      <c r="O109" s="29">
-        <f>SUM(C109:N109)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>Herramientas de IA del equipo</t>
-        </is>
-      </c>
-      <c r="C110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="D110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="E110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="F110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="G110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="H110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="I110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="J110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="K110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="L110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="M110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="N110" s="28">
-        <f>$F$14</f>
-        <v/>
-      </c>
-      <c r="O110" s="29">
-        <f>SUM(C110:N110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>Marketing y contenidos</t>
-        </is>
-      </c>
-      <c r="C111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="D111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="E111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="F111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="G111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="H111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="I111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="J111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="K111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="L111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="M111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="N111" s="28">
-        <f>$F$15</f>
-        <v/>
-      </c>
-      <c r="O111" s="29">
-        <f>SUM(C111:N111)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>Administración</t>
-        </is>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>Estudio contable y legales</t>
-        </is>
-      </c>
-      <c r="C112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="D112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="E112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="F112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="G112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="H112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="I112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="J112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="K112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="L112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="M112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="N112" s="28">
-        <f>$F$16</f>
-        <v/>
-      </c>
-      <c r="O112" s="29">
-        <f>SUM(C112:N112)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>Espacio de trabajo y telefonía</t>
-        </is>
-      </c>
-      <c r="C113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="D113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="E113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="F113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="G113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="H113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="I113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="J113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="K113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="L113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="M113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="N113" s="28">
-        <f>$F$17</f>
-        <v/>
-      </c>
-      <c r="O113" s="29">
-        <f>SUM(C113:N113)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>Conectividad del equipo remoto</t>
-        </is>
-      </c>
-      <c r="C114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="D114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="E114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="F114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="G114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="H114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="I114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="J114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="K114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="L114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="M114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="N114" s="28">
-        <f>$F$18</f>
-        <v/>
-      </c>
-      <c r="O114" s="29">
-        <f>SUM(C114:N114)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>Operación</t>
-        </is>
-      </c>
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>Otros gastos operativos</t>
-        </is>
-      </c>
-      <c r="C115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="D115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="E115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="F115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="G115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="H115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="I115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="J115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="K115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="L115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="M115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="N115" s="28">
-        <f>$F$19</f>
-        <v/>
-      </c>
-      <c r="O115" s="29">
-        <f>SUM(C115:N115)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>COSTOS FIJOS</t>
-        </is>
-      </c>
-      <c r="B116" s="20" t="inlineStr">
-        <is>
-          <t>Total de costos fijos</t>
-        </is>
-      </c>
-      <c r="C116" s="18">
-        <f>SUM(C108:C115)</f>
-        <v/>
-      </c>
-      <c r="D116" s="18">
-        <f>SUM(D108:D115)</f>
-        <v/>
-      </c>
-      <c r="E116" s="18">
-        <f>SUM(E108:E115)</f>
-        <v/>
-      </c>
-      <c r="F116" s="18">
-        <f>SUM(F108:F115)</f>
-        <v/>
-      </c>
-      <c r="G116" s="18">
-        <f>SUM(G108:G115)</f>
-        <v/>
-      </c>
-      <c r="H116" s="18">
-        <f>SUM(H108:H115)</f>
-        <v/>
-      </c>
-      <c r="I116" s="18">
-        <f>SUM(I108:I115)</f>
-        <v/>
-      </c>
-      <c r="J116" s="18">
-        <f>SUM(J108:J115)</f>
-        <v/>
-      </c>
-      <c r="K116" s="18">
-        <f>SUM(K108:K115)</f>
-        <v/>
-      </c>
-      <c r="L116" s="18">
-        <f>SUM(L108:L115)</f>
-        <v/>
-      </c>
-      <c r="M116" s="18">
-        <f>SUM(M108:M115)</f>
-        <v/>
-      </c>
-      <c r="N116" s="18">
-        <f>SUM(N108:N115)</f>
-        <v/>
-      </c>
-      <c r="O116" s="29">
-        <f>SUM(C116:N116)</f>
+      <c r="C75" s="18">
+        <f>SUM(C67:C74)</f>
+        <v/>
+      </c>
+      <c r="D75" s="18">
+        <f>SUM(D67:D74)</f>
+        <v/>
+      </c>
+      <c r="E75" s="18">
+        <f>SUM(E67:E74)</f>
+        <v/>
+      </c>
+      <c r="F75" s="18">
+        <f>SUM(F67:F74)</f>
+        <v/>
+      </c>
+      <c r="G75" s="18">
+        <f>SUM(G67:G74)</f>
+        <v/>
+      </c>
+      <c r="H75" s="18">
+        <f>SUM(H67:H74)</f>
+        <v/>
+      </c>
+      <c r="I75" s="18">
+        <f>SUM(I67:I74)</f>
+        <v/>
+      </c>
+      <c r="J75" s="18">
+        <f>SUM(J67:J74)</f>
+        <v/>
+      </c>
+      <c r="K75" s="18">
+        <f>SUM(K67:K74)</f>
+        <v/>
+      </c>
+      <c r="L75" s="18">
+        <f>SUM(L67:L74)</f>
+        <v/>
+      </c>
+      <c r="M75" s="18">
+        <f>SUM(M67:M74)</f>
+        <v/>
+      </c>
+      <c r="N75" s="18">
+        <f>SUM(N67:N74)</f>
+        <v/>
+      </c>
+      <c r="O75" s="29">
+        <f>SUM(C75:N75)</f>
         <v/>
       </c>
     </row>
